--- a/data/industry/CFM/Flash Wafer.xlsx
+++ b/data/industry/CFM/Flash Wafer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C77821-EA51-43BD-8A53-602CC375ACD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470DE96A-BC01-4294-B045-3CF8FE517231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1TB QLC" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -441,13 +441,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G147"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G159"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="10"/>
     <col min="8" max="16384" width="9" style="7"/>
   </cols>
@@ -3831,6 +3831,282 @@
       </c>
       <c r="G147" s="10">
         <v>28</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C148" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="10">
+        <v>28</v>
+      </c>
+      <c r="F148" s="10">
+        <v>28</v>
+      </c>
+      <c r="G148" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="10">
+        <v>28</v>
+      </c>
+      <c r="F149" s="10">
+        <v>28</v>
+      </c>
+      <c r="G149" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="10">
+        <v>28</v>
+      </c>
+      <c r="F150" s="10">
+        <v>28</v>
+      </c>
+      <c r="G150" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="10">
+        <v>28</v>
+      </c>
+      <c r="F151" s="10">
+        <v>28</v>
+      </c>
+      <c r="G151" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" s="10">
+        <v>28</v>
+      </c>
+      <c r="F152" s="10">
+        <v>28</v>
+      </c>
+      <c r="G152" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" s="10">
+        <v>28</v>
+      </c>
+      <c r="F153" s="10">
+        <v>28</v>
+      </c>
+      <c r="G153" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="10">
+        <v>28</v>
+      </c>
+      <c r="F154" s="10">
+        <v>28</v>
+      </c>
+      <c r="G154" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="10">
+        <v>28</v>
+      </c>
+      <c r="F155" s="10">
+        <v>28</v>
+      </c>
+      <c r="G155" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="10">
+        <v>28</v>
+      </c>
+      <c r="F156" s="10">
+        <v>28</v>
+      </c>
+      <c r="G156" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="10">
+        <v>28</v>
+      </c>
+      <c r="F157" s="10">
+        <v>28</v>
+      </c>
+      <c r="G157" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="10">
+        <v>28</v>
+      </c>
+      <c r="F158" s="10">
+        <v>28</v>
+      </c>
+      <c r="G158" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="10">
+        <v>27</v>
+      </c>
+      <c r="F159" s="10">
+        <v>28</v>
+      </c>
+      <c r="G159" s="10">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3842,13 +4118,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71734CED-25E0-4599-A4D6-BAA4DFE2F205}">
-  <dimension ref="A1:G147"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G159"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="10"/>
     <col min="8" max="16384" width="9" style="7"/>
   </cols>
@@ -7231,6 +7507,282 @@
         <v>29</v>
       </c>
       <c r="G147" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C148" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="10">
+        <v>29</v>
+      </c>
+      <c r="F148" s="10">
+        <v>29</v>
+      </c>
+      <c r="G148" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="10">
+        <v>29</v>
+      </c>
+      <c r="F149" s="10">
+        <v>29</v>
+      </c>
+      <c r="G149" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="10">
+        <v>29</v>
+      </c>
+      <c r="F150" s="10">
+        <v>29</v>
+      </c>
+      <c r="G150" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="10">
+        <v>29</v>
+      </c>
+      <c r="F151" s="10">
+        <v>29</v>
+      </c>
+      <c r="G151" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" s="10">
+        <v>29</v>
+      </c>
+      <c r="F152" s="10">
+        <v>29</v>
+      </c>
+      <c r="G152" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" s="10">
+        <v>29</v>
+      </c>
+      <c r="F153" s="10">
+        <v>29</v>
+      </c>
+      <c r="G153" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="10">
+        <v>29</v>
+      </c>
+      <c r="F154" s="10">
+        <v>29</v>
+      </c>
+      <c r="G154" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="10">
+        <v>29</v>
+      </c>
+      <c r="F155" s="10">
+        <v>29</v>
+      </c>
+      <c r="G155" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="10">
+        <v>29</v>
+      </c>
+      <c r="F156" s="10">
+        <v>29</v>
+      </c>
+      <c r="G156" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="10">
+        <v>29</v>
+      </c>
+      <c r="F157" s="10">
+        <v>29</v>
+      </c>
+      <c r="G157" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="10">
+        <v>29</v>
+      </c>
+      <c r="F158" s="10">
+        <v>29</v>
+      </c>
+      <c r="G158" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="10">
+        <v>29</v>
+      </c>
+      <c r="F159" s="10">
+        <v>29</v>
+      </c>
+      <c r="G159" s="10">
         <v>29</v>
       </c>
     </row>
@@ -7242,13 +7794,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DF3FEF-B1BB-46E2-A380-08118BE83F0E}">
-  <dimension ref="A1:G147"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G159"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="10"/>
     <col min="8" max="16384" width="9" style="7"/>
   </cols>
@@ -10631,6 +11183,282 @@
         <v>23</v>
       </c>
       <c r="G147" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C148" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="10">
+        <v>23</v>
+      </c>
+      <c r="F148" s="10">
+        <v>23</v>
+      </c>
+      <c r="G148" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="10">
+        <v>23</v>
+      </c>
+      <c r="F149" s="10">
+        <v>23</v>
+      </c>
+      <c r="G149" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="10">
+        <v>23</v>
+      </c>
+      <c r="F150" s="10">
+        <v>23</v>
+      </c>
+      <c r="G150" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="10">
+        <v>23</v>
+      </c>
+      <c r="F151" s="10">
+        <v>23</v>
+      </c>
+      <c r="G151" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" s="10">
+        <v>23</v>
+      </c>
+      <c r="F152" s="10">
+        <v>23</v>
+      </c>
+      <c r="G152" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" s="10">
+        <v>23</v>
+      </c>
+      <c r="F153" s="10">
+        <v>23</v>
+      </c>
+      <c r="G153" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="10">
+        <v>23</v>
+      </c>
+      <c r="F154" s="10">
+        <v>23</v>
+      </c>
+      <c r="G154" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="10">
+        <v>23</v>
+      </c>
+      <c r="F155" s="10">
+        <v>23</v>
+      </c>
+      <c r="G155" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="10">
+        <v>23</v>
+      </c>
+      <c r="F156" s="10">
+        <v>23</v>
+      </c>
+      <c r="G156" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="10">
+        <v>23</v>
+      </c>
+      <c r="F157" s="10">
+        <v>23</v>
+      </c>
+      <c r="G157" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="10">
+        <v>23</v>
+      </c>
+      <c r="F158" s="10">
+        <v>23</v>
+      </c>
+      <c r="G158" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="10">
+        <v>23</v>
+      </c>
+      <c r="F159" s="10">
+        <v>23</v>
+      </c>
+      <c r="G159" s="10">
         <v>23</v>
       </c>
     </row>
@@ -10642,13 +11470,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880E409-A6D2-4363-A52D-1827A2E6AA40}">
-  <dimension ref="A1:G147"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G159"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="10"/>
     <col min="8" max="16384" width="9" style="7"/>
   </cols>
@@ -14034,6 +14862,282 @@
         <v>11</v>
       </c>
     </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C148" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="10">
+        <v>11</v>
+      </c>
+      <c r="F148" s="10">
+        <v>11</v>
+      </c>
+      <c r="G148" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="10">
+        <v>11</v>
+      </c>
+      <c r="F149" s="10">
+        <v>11</v>
+      </c>
+      <c r="G149" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="10">
+        <v>11</v>
+      </c>
+      <c r="F150" s="10">
+        <v>11</v>
+      </c>
+      <c r="G150" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="10">
+        <v>11</v>
+      </c>
+      <c r="F151" s="10">
+        <v>11</v>
+      </c>
+      <c r="G151" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46121</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" s="10">
+        <v>11</v>
+      </c>
+      <c r="F152" s="10">
+        <v>11</v>
+      </c>
+      <c r="G152" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46126</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" s="10">
+        <v>11</v>
+      </c>
+      <c r="F153" s="10">
+        <v>11</v>
+      </c>
+      <c r="G153" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="10">
+        <v>11</v>
+      </c>
+      <c r="F154" s="10">
+        <v>11</v>
+      </c>
+      <c r="G154" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46128</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="10">
+        <v>11</v>
+      </c>
+      <c r="F155" s="10">
+        <v>11</v>
+      </c>
+      <c r="G155" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46129</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="10">
+        <v>11</v>
+      </c>
+      <c r="F156" s="10">
+        <v>11</v>
+      </c>
+      <c r="G156" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46132</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="10">
+        <v>11</v>
+      </c>
+      <c r="F157" s="10">
+        <v>11</v>
+      </c>
+      <c r="G157" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B158" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="10">
+        <v>11</v>
+      </c>
+      <c r="F158" s="10">
+        <v>11</v>
+      </c>
+      <c r="G158" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46135</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="10">
+        <v>11</v>
+      </c>
+      <c r="F159" s="10">
+        <v>11</v>
+      </c>
+      <c r="G159" s="10">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/Flash Wafer.xlsx
+++ b/data/industry/CFM/Flash Wafer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/CFM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6AB118-1C2F-B744-8DE1-292D99F01547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27960" yWindow="2520" windowWidth="23040" windowHeight="20120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1TB QLC" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,8 +156,8 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -436,16 +436,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G179"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,7 +468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45866</v>
       </c>
@@ -491,7 +491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45868</v>
       </c>
@@ -537,7 +537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45869</v>
       </c>
@@ -560,7 +560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45870</v>
       </c>
@@ -583,7 +583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45873</v>
       </c>
@@ -606,7 +606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45874</v>
       </c>
@@ -629,7 +629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45875</v>
       </c>
@@ -652,7 +652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45876</v>
       </c>
@@ -675,7 +675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45877</v>
       </c>
@@ -698,7 +698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45880</v>
       </c>
@@ -721,7 +721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45881</v>
       </c>
@@ -744,7 +744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45882</v>
       </c>
@@ -767,7 +767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45883</v>
       </c>
@@ -790,7 +790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45884</v>
       </c>
@@ -813,7 +813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45887</v>
       </c>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45888</v>
       </c>
@@ -859,7 +859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45889</v>
       </c>
@@ -882,7 +882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45890</v>
       </c>
@@ -905,7 +905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>45891</v>
       </c>
@@ -928,7 +928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>45894</v>
       </c>
@@ -951,7 +951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>45895</v>
       </c>
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>45896</v>
       </c>
@@ -997,7 +997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>45897</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <v>45898</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="5">
         <v>45901</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>45902</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <v>45903</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="5">
         <v>45904</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="5">
         <v>45905</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="5">
         <v>45908</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="5">
         <v>45909</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="5">
         <v>45910</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="5">
         <v>45911</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="5">
         <v>45912</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="5">
         <v>45915</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="5">
         <v>45916</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="5">
         <v>45917</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="5">
         <v>45918</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="5">
         <v>45919</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="5">
         <v>45922</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="5">
         <v>45923</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" s="5">
         <v>45924</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" s="5">
         <v>45925</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="5">
         <v>45926</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="5">
         <v>45929</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" s="5">
         <v>45930</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="5">
         <v>45939</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="5">
         <v>45940</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="5">
         <v>45943</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="5">
         <v>45944</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="5">
         <v>45945</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="5">
         <v>45946</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="5">
         <v>45947</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="5">
         <v>45950</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="5">
         <v>45951</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="5">
         <v>45952</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="5">
         <v>45953</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="5">
         <v>45954</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="5">
         <v>45957</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="5">
         <v>45958</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="5">
         <v>45959</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64" s="5">
         <v>45960</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="5">
         <v>45961</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66" s="5">
         <v>45964</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="5">
         <v>45965</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="5">
         <v>45966</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69" s="5">
         <v>45967</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="5">
         <v>45968</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71" s="5">
         <v>45971</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72" s="5">
         <v>45972</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="5">
         <v>45973</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="5">
         <v>45974</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="5">
         <v>45975</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="5">
         <v>45978</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="5">
         <v>45979</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="5">
         <v>45980</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="5">
         <v>45981</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="5">
         <v>45982</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="5">
         <v>45985</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="5">
         <v>45986</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83" s="5">
         <v>45987</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84" s="5">
         <v>45988</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85" s="5">
         <v>45989</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86" s="5">
         <v>45992</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87" s="5">
         <v>45993</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88" s="5">
         <v>45994</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89" s="5">
         <v>45995</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90" s="5">
         <v>45996</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91" s="5">
         <v>45999</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92" s="5">
         <v>46000</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93" s="5">
         <v>46001</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94" s="5">
         <v>46002</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95" s="5">
         <v>46006</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96" s="5">
         <v>46008</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="5">
         <v>46009</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="5">
         <v>46010</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="5">
         <v>46013</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="5">
         <v>46014</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="5">
         <v>46015</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="5">
         <v>46016</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103" s="5">
         <v>46017</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104" s="5">
         <v>46020</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105" s="5">
         <v>46021</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="5">
         <v>46022</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="5">
         <v>46027</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108" s="5">
         <v>46028</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109" s="5">
         <v>46029</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110" s="5">
         <v>46030</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111" s="5">
         <v>46031</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112" s="5">
         <v>46034</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113" s="5">
         <v>46035</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114" s="5">
         <v>46036</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115" s="5">
         <v>46037</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116" s="5">
         <v>46038</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="5">
         <v>46041</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="5">
         <v>46042</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="5">
         <v>46043</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="5">
         <v>46044</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="5">
         <v>46045</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122" s="5">
         <v>46048</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123" s="5">
         <v>46049</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124" s="5">
         <v>46051</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125" s="5">
         <v>46052</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126" s="5">
         <v>46057</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127" s="5">
         <v>46059</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128" s="5">
         <v>46062</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129" s="5">
         <v>46063</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130" s="5">
         <v>46064</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131" s="5">
         <v>46065</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132" s="5">
         <v>46066</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133" s="5">
         <v>46067</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134" s="5">
         <v>46077</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135" s="5">
         <v>46078</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136" s="5">
         <v>46079</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="5">
         <v>46081</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="5">
         <v>46083</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="5">
         <v>46085</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="5">
         <v>46087</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="5">
         <v>46090</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142" s="5">
         <v>46091</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143" s="5">
         <v>46093</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144" s="5">
         <v>46094</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145" s="5">
         <v>46098</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="5">
         <v>46099</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147" s="5">
         <v>46106</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148" s="5">
         <v>46108</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149" s="5">
         <v>46112</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150" s="5">
         <v>46114</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151" s="5">
         <v>46119</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152" s="5">
         <v>46121</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153" s="5">
         <v>46126</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154" s="5">
         <v>46127</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155" s="5">
         <v>46128</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156" s="5">
         <v>46129</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="5">
         <v>46132</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="5">
         <v>46133</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="5">
         <v>46135</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="5">
         <v>46136</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="5">
         <v>46140</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162" s="5">
         <v>46142</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163" s="5">
         <v>46150</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164" s="5">
         <v>46151</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165" s="5">
         <v>46154</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166" s="5">
         <v>46156</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167" s="5">
         <v>46157</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168" s="5">
         <v>46160</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169" s="5">
         <v>46161</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170" s="5">
         <v>46162</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171" s="5">
         <v>46168</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172" s="5">
         <v>46170</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173" s="5">
         <v>46171</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174" s="5">
         <v>46175</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175" s="5">
         <v>46178</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176" s="5">
         <v>46182</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="5">
         <v>46184</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="5">
         <v>46185</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="5">
         <v>46188</v>
       </c>
@@ -4572,16 +4572,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71734CED-25E0-4599-A4D6-BAA4DFE2F205}">
   <dimension ref="A1:G181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.109375" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45866</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45868</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45869</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45870</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45873</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45874</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45875</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45876</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45877</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45880</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45881</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45882</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45883</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45884</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45887</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45888</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45889</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45890</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>45891</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>45894</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>45895</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>45896</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>45897</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <v>45898</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="5">
         <v>45901</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>45902</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <v>45903</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="5">
         <v>45904</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="5">
         <v>45905</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="5">
         <v>45908</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="5">
         <v>45909</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="5">
         <v>45910</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="5">
         <v>45911</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="5">
         <v>45912</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="5">
         <v>45915</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="5">
         <v>45916</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="5">
         <v>45917</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="5">
         <v>45918</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="5">
         <v>45919</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="5">
         <v>45922</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="5">
         <v>45923</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" s="5">
         <v>45924</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" s="5">
         <v>45925</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="5">
         <v>45926</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="5">
         <v>45929</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" s="5">
         <v>45930</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="5">
         <v>45939</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="5">
         <v>45940</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="5">
         <v>45943</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="5">
         <v>45944</v>
       </c>
@@ -5777,7 +5777,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="5">
         <v>45945</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="5">
         <v>45946</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="5">
         <v>45947</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="5">
         <v>45950</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="5">
         <v>45951</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="5">
         <v>45952</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="5">
         <v>45953</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="5">
         <v>45954</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="5">
         <v>45957</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="5">
         <v>45958</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="5">
         <v>45959</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64" s="5">
         <v>45960</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="5">
         <v>45961</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66" s="5">
         <v>45964</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="5">
         <v>45965</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="5">
         <v>45966</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69" s="5">
         <v>45967</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="5">
         <v>45968</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71" s="5">
         <v>45971</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72" s="5">
         <v>45972</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="5">
         <v>45973</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="5">
         <v>45974</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="5">
         <v>45975</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="5">
         <v>45978</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="5">
         <v>45979</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="5">
         <v>45980</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="5">
         <v>45981</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="5">
         <v>45982</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="5">
         <v>45985</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="5">
         <v>45986</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83" s="5">
         <v>45987</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84" s="5">
         <v>45988</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85" s="5">
         <v>45989</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86" s="5">
         <v>45992</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87" s="5">
         <v>45993</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88" s="5">
         <v>45994</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89" s="5">
         <v>45995</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90" s="5">
         <v>45996</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91" s="5">
         <v>45999</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92" s="5">
         <v>46000</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93" s="5">
         <v>46001</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94" s="5">
         <v>46002</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95" s="5">
         <v>46006</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96" s="5">
         <v>46008</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="5">
         <v>46009</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="5">
         <v>46010</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="5">
         <v>46013</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="5">
         <v>46014</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="5">
         <v>46015</v>
       </c>
@@ -6904,7 +6904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="5">
         <v>46016</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103" s="5">
         <v>46017</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104" s="5">
         <v>46020</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105" s="5">
         <v>46021</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="5">
         <v>46022</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="5">
         <v>46027</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108" s="5">
         <v>46028</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109" s="5">
         <v>46029</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110" s="5">
         <v>46030</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111" s="5">
         <v>46031</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112" s="5">
         <v>46034</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113" s="5">
         <v>46035</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114" s="5">
         <v>46036</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115" s="5">
         <v>46037</v>
       </c>
@@ -7226,7 +7226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116" s="5">
         <v>46038</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="5">
         <v>46041</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="5">
         <v>46042</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="5">
         <v>46043</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="5">
         <v>46044</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="5">
         <v>46045</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122" s="5">
         <v>46048</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123" s="5">
         <v>46049</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124" s="5">
         <v>46051</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125" s="5">
         <v>46052</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126" s="5">
         <v>46057</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127" s="5">
         <v>46059</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128" s="5">
         <v>46062</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129" s="5">
         <v>46063</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130" s="5">
         <v>46064</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131" s="5">
         <v>46065</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132" s="5">
         <v>46066</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133" s="5">
         <v>46067</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134" s="5">
         <v>46077</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135" s="5">
         <v>46078</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136" s="5">
         <v>46079</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="5">
         <v>46081</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="5">
         <v>46083</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="5">
         <v>46085</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="5">
         <v>46087</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="5">
         <v>46090</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142" s="5">
         <v>46091</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143" s="5">
         <v>46093</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144" s="5">
         <v>46094</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145" s="5">
         <v>46098</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="5">
         <v>46099</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147" s="5">
         <v>46106</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148" s="5">
         <v>46108</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149" s="5">
         <v>46112</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150" s="5">
         <v>46114</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151" s="5">
         <v>46119</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152" s="5">
         <v>46121</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153" s="5">
         <v>46126</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154" s="5">
         <v>46127</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155" s="5">
         <v>46128</v>
       </c>
@@ -8146,7 +8146,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156" s="5">
         <v>46129</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="5">
         <v>46132</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="5">
         <v>46133</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="5">
         <v>46135</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="5">
         <v>46136</v>
       </c>
@@ -8261,7 +8261,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="5">
         <v>46140</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162" s="5">
         <v>46142</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163" s="5">
         <v>46150</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164" s="5">
         <v>46151</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165" s="5">
         <v>46154</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166" s="5">
         <v>46156</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167" s="5">
         <v>46157</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168" s="5">
         <v>46160</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169" s="5">
         <v>46161</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170" s="5">
         <v>46162</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171" s="5">
         <v>46163</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172" s="5">
         <v>46164</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173" s="5">
         <v>46168</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174" s="5">
         <v>46170</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175" s="5">
         <v>46171</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176" s="5">
         <v>46175</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="5">
         <v>46178</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="5">
         <v>46182</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="5">
         <v>46184</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180" s="5">
         <v>46185</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181" s="5">
         <v>46188</v>
       </c>
@@ -8753,16 +8753,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DF3FEF-B1BB-46E2-A380-08118BE83F0E}">
   <dimension ref="A1:G181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45866</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45868</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45869</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45870</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45873</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45874</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45875</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45876</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45877</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45880</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45881</v>
       </c>
@@ -9061,7 +9061,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45882</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45883</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45884</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45887</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45888</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45889</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45890</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>45891</v>
       </c>
@@ -9245,7 +9245,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>45894</v>
       </c>
@@ -9268,7 +9268,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>45895</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>45896</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>45897</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <v>45898</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="5">
         <v>45901</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>45902</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <v>45903</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="5">
         <v>45904</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="5">
         <v>45905</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="5">
         <v>45908</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="5">
         <v>45909</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="5">
         <v>45910</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="5">
         <v>45911</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="5">
         <v>45912</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="5">
         <v>45915</v>
       </c>
@@ -9613,7 +9613,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="5">
         <v>45916</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="5">
         <v>45917</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="5">
         <v>45918</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="5">
         <v>45919</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="5">
         <v>45922</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="5">
         <v>45923</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" s="5">
         <v>45924</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" s="5">
         <v>45925</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="5">
         <v>45926</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="5">
         <v>45929</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" s="5">
         <v>45930</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="5">
         <v>45939</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="5">
         <v>45940</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="5">
         <v>45943</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="5">
         <v>45944</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="5">
         <v>45945</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="5">
         <v>45946</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="5">
         <v>45947</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="5">
         <v>45950</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="5">
         <v>45951</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="5">
         <v>45952</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="5">
         <v>45953</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="5">
         <v>45954</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="5">
         <v>45957</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="5">
         <v>45958</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="5">
         <v>45959</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64" s="5">
         <v>45960</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="5">
         <v>45961</v>
       </c>
@@ -10257,7 +10257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66" s="5">
         <v>45964</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="5">
         <v>45965</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="5">
         <v>45966</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69" s="5">
         <v>45967</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="5">
         <v>45968</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71" s="5">
         <v>45971</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72" s="5">
         <v>45972</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="5">
         <v>45973</v>
       </c>
@@ -10441,7 +10441,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="5">
         <v>45974</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="5">
         <v>45975</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="5">
         <v>45978</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="5">
         <v>45979</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="5">
         <v>45980</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="5">
         <v>45981</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="5">
         <v>45982</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="5">
         <v>45985</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="5">
         <v>45986</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83" s="5">
         <v>45987</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84" s="5">
         <v>45988</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85" s="5">
         <v>45989</v>
       </c>
@@ -10717,7 +10717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86" s="5">
         <v>45992</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87" s="5">
         <v>45993</v>
       </c>
@@ -10763,7 +10763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88" s="5">
         <v>45994</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89" s="5">
         <v>45995</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90" s="5">
         <v>45996</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91" s="5">
         <v>45999</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92" s="5">
         <v>46000</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93" s="5">
         <v>46001</v>
       </c>
@@ -10901,7 +10901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94" s="5">
         <v>46002</v>
       </c>
@@ -10924,7 +10924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95" s="5">
         <v>46006</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96" s="5">
         <v>46008</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="5">
         <v>46009</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="5">
         <v>46010</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="5">
         <v>46013</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="5">
         <v>46014</v>
       </c>
@@ -11062,7 +11062,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="5">
         <v>46015</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="5">
         <v>46016</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103" s="5">
         <v>46017</v>
       </c>
@@ -11131,7 +11131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104" s="5">
         <v>46020</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105" s="5">
         <v>46021</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="5">
         <v>46022</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="5">
         <v>46027</v>
       </c>
@@ -11223,7 +11223,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108" s="5">
         <v>46028</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109" s="5">
         <v>46029</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110" s="5">
         <v>46030</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111" s="5">
         <v>46031</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112" s="5">
         <v>46034</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113" s="5">
         <v>46035</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114" s="5">
         <v>46036</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115" s="5">
         <v>46037</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116" s="5">
         <v>46038</v>
       </c>
@@ -11430,7 +11430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="5">
         <v>46041</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="5">
         <v>46042</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="5">
         <v>46043</v>
       </c>
@@ -11499,7 +11499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="5">
         <v>46044</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="5">
         <v>46045</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122" s="5">
         <v>46048</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123" s="5">
         <v>46049</v>
       </c>
@@ -11591,7 +11591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124" s="5">
         <v>46051</v>
       </c>
@@ -11614,7 +11614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125" s="5">
         <v>46052</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126" s="5">
         <v>46057</v>
       </c>
@@ -11660,7 +11660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127" s="5">
         <v>46059</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128" s="5">
         <v>46062</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129" s="5">
         <v>46063</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130" s="5">
         <v>46064</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131" s="5">
         <v>46065</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132" s="5">
         <v>46066</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133" s="5">
         <v>46067</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134" s="5">
         <v>46077</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135" s="5">
         <v>46078</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136" s="5">
         <v>46079</v>
       </c>
@@ -11890,7 +11890,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="5">
         <v>46081</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="5">
         <v>46083</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="5">
         <v>46085</v>
       </c>
@@ -11959,7 +11959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="5">
         <v>46087</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="5">
         <v>46090</v>
       </c>
@@ -12005,7 +12005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142" s="5">
         <v>46091</v>
       </c>
@@ -12028,7 +12028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143" s="5">
         <v>46093</v>
       </c>
@@ -12051,7 +12051,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144" s="5">
         <v>46094</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145" s="5">
         <v>46098</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="5">
         <v>46099</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147" s="5">
         <v>46106</v>
       </c>
@@ -12143,7 +12143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148" s="5">
         <v>46108</v>
       </c>
@@ -12166,7 +12166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149" s="5">
         <v>46112</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150" s="5">
         <v>46114</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151" s="5">
         <v>46119</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152" s="5">
         <v>46121</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153" s="5">
         <v>46126</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154" s="5">
         <v>46127</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155" s="5">
         <v>46128</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156" s="5">
         <v>46129</v>
       </c>
@@ -12350,7 +12350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="5">
         <v>46132</v>
       </c>
@@ -12373,7 +12373,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="5">
         <v>46133</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="5">
         <v>46135</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="5">
         <v>46136</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="5">
         <v>46140</v>
       </c>
@@ -12465,7 +12465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162" s="5">
         <v>46142</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163" s="5">
         <v>46150</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164" s="5">
         <v>46151</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165" s="5">
         <v>46154</v>
       </c>
@@ -12557,7 +12557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166" s="5">
         <v>46156</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167" s="5">
         <v>46157</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168" s="5">
         <v>46160</v>
       </c>
@@ -12626,7 +12626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169" s="5">
         <v>46161</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170" s="5">
         <v>46162</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171" s="5">
         <v>46163</v>
       </c>
@@ -12695,7 +12695,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172" s="5">
         <v>46164</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173" s="5">
         <v>46168</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174" s="5">
         <v>46170</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175" s="5">
         <v>46171</v>
       </c>
@@ -12787,7 +12787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176" s="5">
         <v>46175</v>
       </c>
@@ -12810,7 +12810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="5">
         <v>46178</v>
       </c>
@@ -12833,7 +12833,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="5">
         <v>46182</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="5">
         <v>46184</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180" s="5">
         <v>46185</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181" s="5">
         <v>46188</v>
       </c>
@@ -12934,16 +12934,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880E409-A6D2-4363-A52D-1827A2E6AA40}">
   <dimension ref="A1:G181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12966,7 +12966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45866</v>
       </c>
@@ -12989,7 +12989,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45868</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45869</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45870</v>
       </c>
@@ -13081,7 +13081,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45873</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45874</v>
       </c>
@@ -13127,7 +13127,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45875</v>
       </c>
@@ -13150,7 +13150,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45876</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45877</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45880</v>
       </c>
@@ -13219,7 +13219,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45881</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45882</v>
       </c>
@@ -13265,7 +13265,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45883</v>
       </c>
@@ -13288,7 +13288,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45884</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45887</v>
       </c>
@@ -13334,7 +13334,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45888</v>
       </c>
@@ -13357,7 +13357,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45889</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45890</v>
       </c>
@@ -13403,7 +13403,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>45891</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>45894</v>
       </c>
@@ -13449,7 +13449,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>45895</v>
       </c>
@@ -13472,7 +13472,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>45896</v>
       </c>
@@ -13495,7 +13495,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>45897</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <v>45898</v>
       </c>
@@ -13541,7 +13541,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="5">
         <v>45901</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>45902</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <v>45903</v>
       </c>
@@ -13610,7 +13610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="5">
         <v>45904</v>
       </c>
@@ -13633,7 +13633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="5">
         <v>45905</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="5">
         <v>45908</v>
       </c>
@@ -13679,7 +13679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="5">
         <v>45909</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="5">
         <v>45910</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="5">
         <v>45911</v>
       </c>
@@ -13748,7 +13748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="5">
         <v>45912</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="5">
         <v>45915</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="5">
         <v>45916</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="5">
         <v>45917</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="5">
         <v>45918</v>
       </c>
@@ -13863,7 +13863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="5">
         <v>45919</v>
       </c>
@@ -13886,7 +13886,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" s="5">
         <v>45922</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" s="5">
         <v>45923</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" s="5">
         <v>45924</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" s="5">
         <v>45925</v>
       </c>
@@ -13978,7 +13978,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" s="5">
         <v>45926</v>
       </c>
@@ -14001,7 +14001,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" s="5">
         <v>45929</v>
       </c>
@@ -14024,7 +14024,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" s="5">
         <v>45930</v>
       </c>
@@ -14047,7 +14047,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" s="5">
         <v>45939</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" s="5">
         <v>45940</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" s="5">
         <v>45943</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" s="5">
         <v>45944</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53" s="5">
         <v>45945</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54" s="5">
         <v>45946</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55" s="5">
         <v>45947</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56" s="5">
         <v>45950</v>
       </c>
@@ -14231,7 +14231,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="5">
         <v>45951</v>
       </c>
@@ -14254,7 +14254,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="5">
         <v>45952</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="5">
         <v>45953</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="5">
         <v>45954</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="5">
         <v>45957</v>
       </c>
@@ -14346,7 +14346,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62" s="5">
         <v>45958</v>
       </c>
@@ -14369,7 +14369,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63" s="5">
         <v>45959</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64" s="5">
         <v>45960</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65" s="5">
         <v>45961</v>
       </c>
@@ -14438,7 +14438,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66" s="5">
         <v>45964</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67" s="5">
         <v>45965</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68" s="5">
         <v>45966</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69" s="5">
         <v>45967</v>
       </c>
@@ -14530,7 +14530,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70" s="5">
         <v>45968</v>
       </c>
@@ -14553,7 +14553,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71" s="5">
         <v>45971</v>
       </c>
@@ -14576,7 +14576,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72" s="5">
         <v>45972</v>
       </c>
@@ -14599,7 +14599,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73" s="5">
         <v>45973</v>
       </c>
@@ -14622,7 +14622,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74" s="5">
         <v>45974</v>
       </c>
@@ -14645,7 +14645,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75" s="5">
         <v>45975</v>
       </c>
@@ -14668,7 +14668,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76" s="5">
         <v>45978</v>
       </c>
@@ -14691,7 +14691,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="5">
         <v>45979</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="5">
         <v>45980</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="5">
         <v>45981</v>
       </c>
@@ -14760,7 +14760,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="5">
         <v>45982</v>
       </c>
@@ -14783,7 +14783,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="5">
         <v>45985</v>
       </c>
@@ -14806,7 +14806,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82" s="5">
         <v>45986</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83" s="5">
         <v>45987</v>
       </c>
@@ -14852,7 +14852,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84" s="5">
         <v>45988</v>
       </c>
@@ -14875,7 +14875,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85" s="5">
         <v>45989</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86" s="5">
         <v>45992</v>
       </c>
@@ -14921,7 +14921,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87" s="5">
         <v>45993</v>
       </c>
@@ -14944,7 +14944,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88" s="5">
         <v>45994</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89" s="5">
         <v>45995</v>
       </c>
@@ -14990,7 +14990,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90" s="5">
         <v>45996</v>
       </c>
@@ -15013,7 +15013,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91" s="5">
         <v>45999</v>
       </c>
@@ -15036,7 +15036,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92" s="5">
         <v>46000</v>
       </c>
@@ -15059,7 +15059,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93" s="5">
         <v>46001</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94" s="5">
         <v>46002</v>
       </c>
@@ -15105,7 +15105,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95" s="5">
         <v>46006</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96" s="5">
         <v>46008</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="5">
         <v>46009</v>
       </c>
@@ -15174,7 +15174,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="5">
         <v>46010</v>
       </c>
@@ -15197,7 +15197,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="5">
         <v>46013</v>
       </c>
@@ -15220,7 +15220,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="5">
         <v>46014</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="5">
         <v>46015</v>
       </c>
@@ -15266,7 +15266,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102" s="5">
         <v>46016</v>
       </c>
@@ -15289,7 +15289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103" s="5">
         <v>46017</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104" s="5">
         <v>46020</v>
       </c>
@@ -15335,7 +15335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105" s="5">
         <v>46021</v>
       </c>
@@ -15358,7 +15358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106" s="5">
         <v>46022</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107" s="5">
         <v>46027</v>
       </c>
@@ -15404,7 +15404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108" s="5">
         <v>46028</v>
       </c>
@@ -15427,7 +15427,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109" s="5">
         <v>46029</v>
       </c>
@@ -15450,7 +15450,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110" s="5">
         <v>46030</v>
       </c>
@@ -15473,7 +15473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7">
       <c r="A111" s="5">
         <v>46031</v>
       </c>
@@ -15496,7 +15496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112" s="5">
         <v>46034</v>
       </c>
@@ -15519,7 +15519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113" s="5">
         <v>46035</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114" s="5">
         <v>46036</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115" s="5">
         <v>46037</v>
       </c>
@@ -15588,7 +15588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116" s="5">
         <v>46038</v>
       </c>
@@ -15611,7 +15611,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="5">
         <v>46041</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="5">
         <v>46042</v>
       </c>
@@ -15657,7 +15657,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="5">
         <v>46043</v>
       </c>
@@ -15680,7 +15680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="5">
         <v>46044</v>
       </c>
@@ -15703,7 +15703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="5">
         <v>46045</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122" s="5">
         <v>46048</v>
       </c>
@@ -15749,7 +15749,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123" s="5">
         <v>46049</v>
       </c>
@@ -15772,7 +15772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124" s="5">
         <v>46051</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125" s="5">
         <v>46052</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126" s="5">
         <v>46057</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127" s="5">
         <v>46059</v>
       </c>
@@ -15864,7 +15864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128" s="5">
         <v>46062</v>
       </c>
@@ -15887,7 +15887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129" s="5">
         <v>46063</v>
       </c>
@@ -15910,7 +15910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130" s="5">
         <v>46064</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131" s="5">
         <v>46065</v>
       </c>
@@ -15956,7 +15956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132" s="5">
         <v>46066</v>
       </c>
@@ -15979,7 +15979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133" s="5">
         <v>46067</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134" s="5">
         <v>46077</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135" s="5">
         <v>46078</v>
       </c>
@@ -16048,7 +16048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136" s="5">
         <v>46079</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="5">
         <v>46081</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="5">
         <v>46083</v>
       </c>
@@ -16117,7 +16117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="5">
         <v>46085</v>
       </c>
@@ -16140,7 +16140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="5">
         <v>46087</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="5">
         <v>46090</v>
       </c>
@@ -16186,7 +16186,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142" s="5">
         <v>46091</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143" s="5">
         <v>46093</v>
       </c>
@@ -16232,7 +16232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144" s="5">
         <v>46094</v>
       </c>
@@ -16255,7 +16255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145" s="5">
         <v>46098</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="5">
         <v>46099</v>
       </c>
@@ -16301,7 +16301,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147" s="5">
         <v>46106</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148" s="5">
         <v>46108</v>
       </c>
@@ -16347,7 +16347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149" s="5">
         <v>46112</v>
       </c>
@@ -16370,7 +16370,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7">
       <c r="A150" s="5">
         <v>46114</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7">
       <c r="A151" s="5">
         <v>46119</v>
       </c>
@@ -16416,7 +16416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7">
       <c r="A152" s="5">
         <v>46121</v>
       </c>
@@ -16439,7 +16439,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7">
       <c r="A153" s="5">
         <v>46126</v>
       </c>
@@ -16462,7 +16462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7">
       <c r="A154" s="5">
         <v>46127</v>
       </c>
@@ -16485,7 +16485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155" s="5">
         <v>46128</v>
       </c>
@@ -16508,7 +16508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156" s="5">
         <v>46129</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="5">
         <v>46132</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="5">
         <v>46133</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="5">
         <v>46135</v>
       </c>
@@ -16600,7 +16600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="5">
         <v>46136</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="5">
         <v>46140</v>
       </c>
@@ -16646,7 +16646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162" s="5">
         <v>46142</v>
       </c>
@@ -16669,7 +16669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163" s="5">
         <v>46150</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164" s="5">
         <v>46151</v>
       </c>
@@ -16715,7 +16715,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165" s="5">
         <v>46154</v>
       </c>
@@ -16738,7 +16738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166" s="5">
         <v>46156</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167" s="5">
         <v>46157</v>
       </c>
@@ -16784,7 +16784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168" s="5">
         <v>46160</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169" s="5">
         <v>46161</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170" s="5">
         <v>46162</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171" s="5">
         <v>46163</v>
       </c>
@@ -16876,7 +16876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172" s="5">
         <v>46164</v>
       </c>
@@ -16899,7 +16899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173" s="5">
         <v>46168</v>
       </c>
@@ -16922,7 +16922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174" s="5">
         <v>46170</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175" s="5">
         <v>46171</v>
       </c>
@@ -16968,7 +16968,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176" s="5">
         <v>46175</v>
       </c>
@@ -16991,7 +16991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="5">
         <v>46178</v>
       </c>
@@ -17014,7 +17014,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="5">
         <v>46182</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="5">
         <v>46184</v>
       </c>
@@ -17060,7 +17060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180" s="5">
         <v>46185</v>
       </c>
@@ -17083,7 +17083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181" s="5">
         <v>46188</v>
       </c>

--- a/data/industry/CFM/Flash Wafer.xlsx
+++ b/data/industry/CFM/Flash Wafer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6AB118-1C2F-B744-8DE1-292D99F01547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020F18FF-5966-49E9-801D-2E1712039308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1TB QLC" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" style="5" bestFit="1" customWidth="1"/>
@@ -4562,6 +4562,167 @@
         <v>27</v>
       </c>
     </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="5">
+        <v>46189</v>
+      </c>
+      <c r="B180" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C180" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" s="9">
+        <v>27</v>
+      </c>
+      <c r="F180" s="9">
+        <v>27</v>
+      </c>
+      <c r="G180" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B181" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C181" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" s="9">
+        <v>27</v>
+      </c>
+      <c r="F181" s="9">
+        <v>27</v>
+      </c>
+      <c r="G181" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="5">
+        <v>46191</v>
+      </c>
+      <c r="B182" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C182" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="9">
+        <v>27</v>
+      </c>
+      <c r="F182" s="9">
+        <v>27</v>
+      </c>
+      <c r="G182" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="5">
+        <v>46195</v>
+      </c>
+      <c r="B183" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C183" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="9">
+        <v>27</v>
+      </c>
+      <c r="F183" s="9">
+        <v>27</v>
+      </c>
+      <c r="G183" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B184" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C184" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="F184" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="G184" s="9">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B185" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C185" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="F185" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="G185" s="9">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="5">
+        <v>46202</v>
+      </c>
+      <c r="B186" s="5">
+        <v>46202</v>
+      </c>
+      <c r="C186" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="F186" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="G186" s="9">
+        <v>26.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4571,7 +4732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71734CED-25E0-4599-A4D6-BAA4DFE2F205}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="5" bestFit="1" customWidth="1"/>
@@ -8744,6 +8905,167 @@
         <v>29</v>
       </c>
     </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="5">
+        <v>46189</v>
+      </c>
+      <c r="B182" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C182" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="9">
+        <v>29</v>
+      </c>
+      <c r="F182" s="9">
+        <v>29</v>
+      </c>
+      <c r="G182" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B183" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C183" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="9">
+        <v>29</v>
+      </c>
+      <c r="F183" s="9">
+        <v>29</v>
+      </c>
+      <c r="G183" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="5">
+        <v>46191</v>
+      </c>
+      <c r="B184" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C184" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="9">
+        <v>29</v>
+      </c>
+      <c r="F184" s="9">
+        <v>29</v>
+      </c>
+      <c r="G184" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="5">
+        <v>46195</v>
+      </c>
+      <c r="B185" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C185" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="9">
+        <v>29</v>
+      </c>
+      <c r="F185" s="9">
+        <v>29</v>
+      </c>
+      <c r="G185" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B186" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C186" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="9">
+        <v>29</v>
+      </c>
+      <c r="F186" s="9">
+        <v>29</v>
+      </c>
+      <c r="G186" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B187" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C187" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="9">
+        <v>29</v>
+      </c>
+      <c r="F187" s="9">
+        <v>29</v>
+      </c>
+      <c r="G187" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="5">
+        <v>46202</v>
+      </c>
+      <c r="B188" s="5">
+        <v>46202</v>
+      </c>
+      <c r="C188" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="9">
+        <v>29</v>
+      </c>
+      <c r="F188" s="9">
+        <v>29</v>
+      </c>
+      <c r="G188" s="9">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8752,7 +9074,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DF3FEF-B1BB-46E2-A380-08118BE83F0E}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -12925,6 +13247,167 @@
         <v>23</v>
       </c>
     </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="5">
+        <v>46189</v>
+      </c>
+      <c r="B182" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C182" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="9">
+        <v>23</v>
+      </c>
+      <c r="F182" s="9">
+        <v>23</v>
+      </c>
+      <c r="G182" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B183" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C183" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="9">
+        <v>23</v>
+      </c>
+      <c r="F183" s="9">
+        <v>23</v>
+      </c>
+      <c r="G183" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="5">
+        <v>46191</v>
+      </c>
+      <c r="B184" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C184" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="9">
+        <v>23</v>
+      </c>
+      <c r="F184" s="9">
+        <v>23</v>
+      </c>
+      <c r="G184" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="5">
+        <v>46195</v>
+      </c>
+      <c r="B185" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C185" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="9">
+        <v>23</v>
+      </c>
+      <c r="F185" s="9">
+        <v>23</v>
+      </c>
+      <c r="G185" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B186" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C186" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="F186" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="G186" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B187" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C187" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="F187" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="G187" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="5">
+        <v>46202</v>
+      </c>
+      <c r="B188" s="5">
+        <v>46202</v>
+      </c>
+      <c r="C188" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="F188" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="G188" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12933,7 +13416,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880E409-A6D2-4363-A52D-1827A2E6AA40}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -17106,6 +17589,167 @@
         <v>11</v>
       </c>
     </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="5">
+        <v>46189</v>
+      </c>
+      <c r="B182" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C182" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="9">
+        <v>11</v>
+      </c>
+      <c r="F182" s="9">
+        <v>11</v>
+      </c>
+      <c r="G182" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="5">
+        <v>46190</v>
+      </c>
+      <c r="B183" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C183" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="9">
+        <v>11</v>
+      </c>
+      <c r="F183" s="9">
+        <v>11</v>
+      </c>
+      <c r="G183" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="5">
+        <v>46191</v>
+      </c>
+      <c r="B184" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C184" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="9">
+        <v>11</v>
+      </c>
+      <c r="F184" s="9">
+        <v>11</v>
+      </c>
+      <c r="G184" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="5">
+        <v>46195</v>
+      </c>
+      <c r="B185" s="5">
+        <v>46195</v>
+      </c>
+      <c r="C185" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="9">
+        <v>11</v>
+      </c>
+      <c r="F185" s="9">
+        <v>11</v>
+      </c>
+      <c r="G185" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B186" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C186" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="9">
+        <v>11</v>
+      </c>
+      <c r="F186" s="9">
+        <v>11</v>
+      </c>
+      <c r="G186" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B187" s="5">
+        <v>46198</v>
+      </c>
+      <c r="C187" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="9">
+        <v>11</v>
+      </c>
+      <c r="F187" s="9">
+        <v>11</v>
+      </c>
+      <c r="G187" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="5">
+        <v>46202</v>
+      </c>
+      <c r="B188" s="5">
+        <v>46202</v>
+      </c>
+      <c r="C188" s="6">
+        <v>0.75694444444444497</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="9">
+        <v>11</v>
+      </c>
+      <c r="F188" s="9">
+        <v>11</v>
+      </c>
+      <c r="G188" s="9">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
